--- a/RobotOnTheFloor/RNN_Ts7/Odometry.xlsx
+++ b/RobotOnTheFloor/RNN_Ts7/Odometry.xlsx
@@ -491,22 +491,22 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7674052337799995</v>
+        <v>-1.1832607718423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1792502264089079</v>
+        <v>0.2214262921613218</v>
       </c>
       <c r="G2" t="n">
-        <v>-8.555762761503582</v>
+        <v>-1.867257613998291</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7613901279246555</v>
+        <v>0.2284591712877135</v>
       </c>
       <c r="I2" t="n">
-        <v>-47.02074738455748</v>
+        <v>-10.1832343571131</v>
       </c>
       <c r="J2" t="n">
-        <v>13.53381469234261</v>
+        <v>3.151800621472202</v>
       </c>
     </row>
     <row r="3">
@@ -525,22 +525,22 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>-25.82520757130134</v>
+        <v>-3.235013787688947</v>
       </c>
       <c r="F3" t="n">
-        <v>2.72061236366139</v>
+        <v>0.4295150686322932</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4994451702037199</v>
+        <v>-1.636868420627287</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1194737435881862</v>
+        <v>0.210102074968842</v>
       </c>
       <c r="I3" t="n">
-        <v>-242.0270003073229</v>
+        <v>-59.72019647691581</v>
       </c>
       <c r="J3" t="n">
-        <v>68.49294454031971</v>
+        <v>17.11293413699513</v>
       </c>
     </row>
     <row r="4">
@@ -559,22 +559,22 @@
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.023193693786407</v>
+        <v>0.4346860623774202</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4080322761949405</v>
+        <v>0.05733413558713735</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.16084162339815</v>
+        <v>-0.8912281413392031</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2518515442518179</v>
+        <v>0.1506904757273808</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.26158081397136</v>
+        <v>-1.175919191126482</v>
       </c>
       <c r="J4" t="n">
-        <v>2.046550594532452</v>
+        <v>0.6132450809728106</v>
       </c>
     </row>
     <row r="5">
@@ -593,22 +593,22 @@
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4300062969894747</v>
+        <v>0.9276433790948477</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05780875735994706</v>
+        <v>0.00733840798450783</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1990223076489971</v>
+        <v>0.114606267796712</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06382080874807797</v>
+        <v>0.07054696352883048</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.970731368700427</v>
+        <v>0.4372573054709662</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8372491065736754</v>
+        <v>0.1585992672341181</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>-47.41076075253515</v>
+        <v>-51.74580271331673</v>
       </c>
       <c r="F6" t="n">
-        <v>4.51142540482051</v>
+        <v>4.915410348019503</v>
       </c>
       <c r="G6" t="n">
-        <v>-13.81656897942085</v>
+        <v>-30.09594875229539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7753298390018669</v>
+        <v>1.627206472241584</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.67862022458863</v>
+        <v>-0.3896218638301199</v>
       </c>
       <c r="J6" t="n">
-        <v>19.72956116107066</v>
+        <v>4.105133789799535</v>
       </c>
     </row>
     <row r="7">
@@ -661,22 +661,22 @@
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>-27.41918629657788</v>
+        <v>-10.93523098156217</v>
       </c>
       <c r="F7" t="n">
-        <v>2.648399592357042</v>
+        <v>1.112250735696209</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.053701588296373</v>
+        <v>-1.596154763224999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2644529677727362</v>
+        <v>0.1358530613525243</v>
       </c>
       <c r="I7" t="n">
-        <v>-90.76867125226487</v>
+        <v>-18.01800026858782</v>
       </c>
       <c r="J7" t="n">
-        <v>271.0972553096875</v>
+        <v>56.18178408751681</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.729429375345505</v>
+        <v>-5.996840395785333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2543570237935633</v>
+        <v>0.6520394024869217</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.198873914053069</v>
+        <v>-6.559486089048442</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4290353320399989</v>
+        <v>0.3955770826902923</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04002065399878341</v>
+        <v>0.1768915056132067</v>
       </c>
       <c r="J8" t="n">
-        <v>2.835910799443941</v>
+        <v>2.431575510524151</v>
       </c>
     </row>
     <row r="9">
@@ -729,22 +729,22 @@
         <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.725060546668085</v>
+        <v>-7.621931206599978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.440330989602083</v>
+        <v>0.8034825084221165</v>
       </c>
       <c r="G9" t="n">
-        <v>-19.73882839169146</v>
+        <v>-7.483045469546044</v>
       </c>
       <c r="H9" t="n">
-        <v>1.085233194024249</v>
+        <v>0.4439056226366476</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2964512085255019</v>
+        <v>0.189439265489847</v>
       </c>
       <c r="J9" t="n">
-        <v>2.078379731802828</v>
+        <v>2.394507704960188</v>
       </c>
     </row>
     <row r="10">
@@ -763,22 +763,22 @@
         <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.113835081688419</v>
+        <v>-0.3164797448262424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1679894729636991</v>
+        <v>0.1046225130884378</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6567960981600649</v>
+        <v>-2.219449091545111</v>
       </c>
       <c r="H10" t="n">
-        <v>0.09817559940096425</v>
+        <v>0.1907726271532992</v>
       </c>
       <c r="I10" t="n">
-        <v>-250.4444611836828</v>
+        <v>-64.97113393566148</v>
       </c>
       <c r="J10" t="n">
-        <v>100.3934405531024</v>
+        <v>26.34008751599568</v>
       </c>
     </row>
     <row r="11">
@@ -797,22 +797,22 @@
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.89627669201288</v>
+        <v>-2.16941143965002</v>
       </c>
       <c r="F11" t="n">
-        <v>1.024885405419067</v>
+        <v>0.2518776237390528</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.173032131026448</v>
+        <v>-1.015485432665295</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1287658343823944</v>
+        <v>0.1194302006478473</v>
       </c>
       <c r="I11" t="n">
-        <v>-224.0271774784733</v>
+        <v>-59.17674836145322</v>
       </c>
       <c r="J11" t="n">
-        <v>89.84589463084005</v>
+        <v>24.02658138049532</v>
       </c>
     </row>
     <row r="12">
@@ -831,22 +831,22 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2155223842064282</v>
+        <v>-3.845444413266208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06234354911156045</v>
+        <v>0.3850743420387004</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.197922299755247</v>
+        <v>-5.628374257091367</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1302407335790154</v>
+        <v>0.3927729045635385</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.418322500208501</v>
+        <v>0.2152430772954038</v>
       </c>
       <c r="J12" t="n">
-        <v>1.364822892103079</v>
+        <v>0.3133274326159308</v>
       </c>
     </row>
     <row r="13">
@@ -865,22 +865,22 @@
         <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.450999762608806</v>
+        <v>0.3385131052660693</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1947844285117679</v>
+        <v>0.0525693020147948</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.076433647142005</v>
+        <v>-2.067267629019622</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3008106529710333</v>
+        <v>0.1817549174195866</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.927613352884546</v>
+        <v>-0.9903478538983319</v>
       </c>
       <c r="J13" t="n">
-        <v>2.76596643268126</v>
+        <v>0.7946799385028727</v>
       </c>
     </row>
     <row r="14">
@@ -899,22 +899,22 @@
         <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7195178623751399</v>
+        <v>-3.154550616880064</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1595139909636443</v>
+        <v>0.3854039344747609</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.37142265967272</v>
+        <v>-14.2585821053469</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3234687219506416</v>
+        <v>1.129077290541615</v>
       </c>
       <c r="I14" t="n">
-        <v>-141.6864044240956</v>
+        <v>-35.85988745106036</v>
       </c>
       <c r="J14" t="n">
-        <v>47.2930565300563</v>
+        <v>12.21711870833387</v>
       </c>
     </row>
     <row r="15">
@@ -933,22 +933,22 @@
         <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.91069270832004</v>
+        <v>-5.031527660192972</v>
       </c>
       <c r="F15" t="n">
-        <v>2.589182748188696</v>
+        <v>0.5595248934233474</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.697703815180763</v>
+        <v>-1.142075917143642</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1996198659415887</v>
+        <v>0.1585055056862377</v>
       </c>
       <c r="I15" t="n">
-        <v>-173.2229113965905</v>
+        <v>-44.63309277883788</v>
       </c>
       <c r="J15" t="n">
-        <v>57.74575391934486</v>
+        <v>15.12497595788067</v>
       </c>
     </row>
     <row r="16">
@@ -967,22 +967,22 @@
         <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.958778987993865</v>
+        <v>-0.0947922680395541</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9238430238261832</v>
+        <v>0.1015602616130485</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.869537734613989</v>
+        <v>-5.78035415344358</v>
       </c>
       <c r="H16" t="n">
-        <v>0.286331138167518</v>
+        <v>0.5017205297076726</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.1164061872746</v>
+        <v>-2.974473324617886</v>
       </c>
       <c r="J16" t="n">
-        <v>5.010295516461584</v>
+        <v>1.317329372598674</v>
       </c>
     </row>
     <row r="17">
@@ -1001,22 +1001,22 @@
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2064631434503328</v>
+        <v>0.8181335752877387</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1119195997746028</v>
+        <v>0.01687114735061293</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2629587267337241</v>
+        <v>0.6162923756773386</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05453826299792416</v>
+        <v>0.02839291107386551</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9630113812566885</v>
+        <v>0.4072108402779612</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6506352766938112</v>
+        <v>0.1964785037109302</v>
       </c>
     </row>
   </sheetData>
